--- a/Equipments/Transport_to_Aachen/DACNV_輸出手続き_発送_振動対策.xlsx
+++ b/Equipments/Transport_to_Aachen/DACNV_輸出手続き_発送_振動対策.xlsx
@@ -15,7 +15,12 @@
     <sheet name="該非判定書_追跡表" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'判定リードタイム'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'発送サービス比較'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'振動対策・梱包'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'時系列チェックリスト'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'該非判定書_追跡表'!$A$4:$L$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'該非判定書_追跡表'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -565,7 +570,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1032,7 +1037,16 @@
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="B23:H23"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1040,7 +1054,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1372,7 +1386,16 @@
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1380,7 +1403,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1680,7 +1703,16 @@
   <mergeCells count="1">
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1688,7 +1720,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2251,7 +2283,16 @@
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2259,7 +2300,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2584,7 +2625,16 @@
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2592,7 +2642,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3558,6 +3608,15 @@
       <formula1>"未着手,請求済,督促中,受領,輸出管理室提出済,完了,自己判定へ切替"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Equipments/Transport_to_Aachen/DACNV_輸出手続き_発送_振動対策.xlsx
+++ b/Equipments/Transport_to_Aachen/DACNV_輸出手続き_発送_振動対策.xlsx
@@ -575,14 +575,14 @@
   <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1019,7 +1019,7 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>最短：全品目が非該当と確認できた場合 → 該非判定書の収集に3〜4週間、輸出管理室の審査に1〜2週間、合わせて1〜1.5ヶ月。 最悪：SynthHD が該当かつ少額特例も包括許可も使えない場合 → 判定書に1ヶ月、許可申請の標準処理期間が原則90日以内（実務上は3〜6週間程度）で、合計3〜4ヶ月を見ておく。渡航日が決まっているなら、逆算して最低でも3ヶ月前には動き始めること。</t>
@@ -1038,7 +1038,7 @@
     <mergeCell ref="B23:H23"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
@@ -1059,14 +1059,14 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1342,35 +1342,35 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>1. 光学部品・マイクロ波部品・ケーブル類の小物 → DHL または FedEx で2〜3箱に分けて発送。1箱に集中させず分散させると、1箱失っても実験が止まらない。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1">
+    <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2. ステージ・DC電源・柱・黒い板などの重量物 → 航空フォワーダーの混載便。木枠梱包を依頼する。見積取得から出荷まで3〜4週間見ておく。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>3. ミスミのオーダーメイド治具 → 図面データを必ず手元にも保存したうえで発送。紛失しても現地または帰国後に再製作できる状態にしておく。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>4. レーザー、マイクロ波アンプ、ダイヤモンドアンビル、BeCu DAC、CMOSカメラ、対物レンズ → 発送せず手荷物。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>5. アラルダイトと一部の消耗品 → 送らずドイツで購入。</t>
@@ -1387,7 +1387,7 @@
     <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
@@ -1408,9 +1408,9 @@
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="95" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1725,11 +1725,11 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2306,7 +2306,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="118" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2330,7 +2330,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5">
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>集め方が群ごとに全く違う。ここを飛ばして片っ端から問い合わせると、出るはずのないところに催促し、自力で片付く分を放置することになる。</t>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>CNI（レーザー）、Mini-Circuits（アンプ、ターミネータ）、Windfreak（SynthHD）、菊水（DC電源）、シグマ光機（ステージ）、Pasternack（サーキュレータ）、Thorlabs、Mitutoyo。通常の請求ルートで進む。所要2〜4週間。</t>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>ベリリウム銅DAC、NV注入ダイヤモンドアンビル、対向ダイヤモンドアンビル、ジルコニア台座、ガスケット。「待てば来る」ではなく「取れないかもしれない」タイプ。ステップ4の代替ルートで処理する。最も詰まりやすいので最初に着手する。</t>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12">
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>DAC固定器具（型番「不明」）、アイリス、チューブ×2、柱、黒い板、白金箔、エナメル線、はんだごて、テープ、アラルダイト。外部待ちがゼロで自分たちだけで潰せる唯一の群。現物とラベル、発注履歴、納品書を当たれば確定する。先に片付けてしまうと後半が楽になる。</t>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="45" customHeight="1">
+    <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Thorlabs と Mini-Circuits は製品ページに ECCN を掲載している。問い合わせを待たずに型番ごとに拾って一覧化できる。ただし ECCN は米国法の分類であり、日本の輸出令の該非判定そのものではない点に注意（ステップ3参照）。</t>
@@ -2400,35 +2400,35 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1">
+    <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>メーカーに投げる前に必ずここを通す。理由は三つある。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
+    <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>・同じ型番の判定を学内の誰かが過去にやっていれば、その判定書をそのまま流用できることがある。Thorlabs や Mini-Circuits の汎用品は特に可能性が高い。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20">
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>・機関が一般包括許可・特別一般包括許可を持っていれば、グループA向けの手続きが大幅に短縮される。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>・提出様式が機関ごとに決まっている。様式を知らずに集めると、集め直しになる。</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1">
+    <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>この相談を後回しにすると二度手間が確定するので、着手日に済ませること。</t>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>国内メーカー（菊水、シグマ光機、Mitutoyo）向けは、日本語で型番を指定して「該非判定書（パラメータシート）をいただきたい」と書けば通じる。国内メーカーはこの依頼に慣れており、様式も日本の輸出令に沿ったものが出てくる。</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="45" customHeight="1">
+    <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>海外メーカー向けは、ECCN と日本の輸出令に対する判定の両方を明示的に聞く。片方しか出ないことが多いため、最初から両方書いておかないと往復が一回増える。用途（大学の基礎研究）、仕向地（ドイツ）、非軍事用途である旨を書くと回答が早くなる。</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="420" customHeight="1">
+    <row r="30">
       <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Subject: Request for export control classification (ECCN / Japanese ECCN) - [model number]
@@ -2481,7 +2481,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32">
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>最後の「出せないなら出せないと言ってほしい」の一文が効く。これが無いと返事が来ないまま待ち続けることになり、自己判定への切り替え判断が遅れる。</t>
@@ -2495,42 +2495,42 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1">
+    <row r="36">
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>届いた書類がそのまま使えるとは限らない。提出前に以下を確認する。</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1">
+    <row r="38">
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>・型番が発注品と完全に一致しているか。末尾の記号違い（-ML、/M など）は別製品扱いになり得る。</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1">
+    <row r="39">
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>・発行日と発行者名（会社名・担当者）が入っているか。日付の無い書類は受理されないことがある。</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
+    <row r="40">
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>・判定の根拠が書かれているか。該当なら項番、非該当なら「どの基準を下回るから非該当か」。結論だけの書類は根拠として弱い。</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41">
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>・「EAR99」だけの回答で満足しないこと。これは米国輸出管理法上の分類であって、日本の輸出令別表第1に対する判定ではない。参考にはなるが、そのままでは日本の申請の根拠にならない。この取り違えは非常に多い。</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
+    <row r="42">
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>・仕様のバージョン違いに注意。同じ型番でも製造時期で仕様が変わっている場合があるため、手元の個体のシリアルや購入時期と、判定書が対象としている仕様が一致するかを見る。</t>
@@ -2544,42 +2544,42 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="15" customHeight="1">
+    <row r="45">
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>群IIと、群Iで回答が得られなかった品目はこちらに回す。上から順に試す。</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47">
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>・公開仕様書のパラメータを、貨物等省令の該当条文の判定基準と自分で突き合わせて自己判定する。レーザーなら波長・出力・パルス幅、アンプなら動作周波数帯と出力、という具合に条文が要求している値を一つずつ拾って対比表を作る。</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48">
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>・作った自己判定を輸出管理室に諮り、機関としての判断を仰ぐ。最終的に責任を持つのは機関なので、自分たちだけで結論を出さない。</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
+    <row r="49">
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>・CISTEC の解説書・項目別対比表を使って根拠を文書化する。自己判定の様式として実務上広く使われており、輸出管理室も見慣れている。</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50">
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>・ベリリウム銅DACのように材質が争点の場合は、借用元の購入記録 → 製作元 → それでも不明なら成分分析、という順にたどる。分析は数週間かかるので早く着手を判断する。</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51">
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>・どうしても根拠が作れない品目は、その一点だけ現地調達に切り替える判断も選択肢に入れる。一品目のために全体のスケジュールを止めない。</t>
@@ -2593,14 +2593,14 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="45" customHeight="1">
+    <row r="54">
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>典型的な失敗は「依頼しっぱなしで止まる」こと。誰にいつ何を頼んだかを一覧にしておかないと、返事が来ていないこと自体に気づけない。次シートの追跡表を使い、請求から2週間返答が無ければ督促する、という運用をあらかじめ決めておく。</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="30" customHeight="1">
+    <row r="56">
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>督促は遠慮しなくてよい。海外メーカーの窓口は問い合わせを大量に捌いており、一度で返ってこないのは珍しくない。件名に元のやりとりを引用して短く再送するのが有効。</t>
@@ -2614,7 +2614,7 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
+    <row r="60">
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>本手順は一般的な進め方であり、最終的な該非判定の責任は所属機関にある。判断に迷う点は必ず輸出管理室に確認すること。</t>
@@ -2647,18 +2647,18 @@
   <dimension ref="A1:L29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3609,7 +3609,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;C&amp;P / &amp;N ページ&amp;R&amp;D</oddFooter>
